--- a/AI Planning/Job Scheduling/Flow Shop/problemset/solution/def/pizzeria-50j-4m-5_60tr-exponentiald_def.xlsx
+++ b/AI Planning/Job Scheduling/Flow Shop/problemset/solution/def/pizzeria-50j-4m-5_60tr-exponentiald_def.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
         <v>40</v>
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
         <v>79</v>
@@ -836,7 +836,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
+        <v>115</v>
+      </c>
+      <c r="E21" t="n">
         <v>124</v>
-      </c>
-      <c r="E21" t="n">
-        <v>136</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E24" t="n">
         <v>109</v>
@@ -941,7 +941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E25" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
+        <v>71</v>
+      </c>
+      <c r="E26" t="n">
         <v>78</v>
-      </c>
-      <c r="E26" t="n">
-        <v>89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E27" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>109</v>
       </c>
       <c r="E28" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E29" t="n">
         <v>149</v>
@@ -1046,7 +1046,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
+        <v>78</v>
+      </c>
+      <c r="E30" t="n">
         <v>89</v>
-      </c>
-      <c r="E30" t="n">
-        <v>104</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E31" t="n">
         <v>128</v>
@@ -1088,7 +1088,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
         <v>128</v>
       </c>
       <c r="E32" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E33" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
         <v>128</v>
       </c>
       <c r="E35" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E36" t="n">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="E37" t="n">
-        <v>237</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
+        <v>105</v>
+      </c>
+      <c r="E38" t="n">
         <v>112</v>
-      </c>
-      <c r="E38" t="n">
-        <v>131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E39" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="E40" t="n">
-        <v>197</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D41" t="n">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="E41" t="n">
-        <v>257</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E42" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E43" t="n">
-        <v>181</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="E44" t="n">
-        <v>232</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="E45" t="n">
-        <v>266</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="E46" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D47" t="n">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E47" t="n">
-        <v>216</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="E48" t="n">
-        <v>247</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="E49" t="n">
-        <v>278</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D50" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="E50" t="n">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D51" t="n">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="E51" t="n">
-        <v>221</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D52" t="n">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="E52" t="n">
-        <v>259</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D53" t="n">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="E53" t="n">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="E54" t="n">
-        <v>200</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="E55" t="n">
-        <v>239</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="E56" t="n">
-        <v>276</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E57" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="E58" t="n">
-        <v>212</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D59" t="n">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="E59" t="n">
-        <v>252</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D60" t="n">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="E60" t="n">
-        <v>296</v>
+        <v>242</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1706,19 +1706,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
+        <v>291</v>
+      </c>
+      <c r="E61" t="n">
         <v>296</v>
-      </c>
-      <c r="E61" t="n">
-        <v>304</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="E62" t="n">
-        <v>241</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1748,19 +1748,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D63" t="n">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="E63" t="n">
-        <v>260</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1772,16 +1772,16 @@
         <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="E64" t="n">
-        <v>303</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1790,19 +1790,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D65" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E65" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1811,19 +1811,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D66" t="n">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="E66" t="n">
-        <v>251</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D67" t="n">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="E67" t="n">
-        <v>287</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1853,19 +1853,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="E68" t="n">
-        <v>313</v>
+        <v>263</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1874,19 +1874,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E69" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1895,19 +1895,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D70" t="n">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="E70" t="n">
-        <v>256</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="E71" t="n">
-        <v>292</v>
+        <v>269</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1937,19 +1937,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="E72" t="n">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1958,19 +1958,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="E73" t="n">
-        <v>369</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1979,19 +1979,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D74" t="n">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="E74" t="n">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2000,19 +2000,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D75" t="n">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="E75" t="n">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2021,19 +2021,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D76" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="E76" t="n">
-        <v>368</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2042,19 +2042,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="E77" t="n">
-        <v>378</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="E78" t="n">
-        <v>329</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2084,19 +2084,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>329</v>
+        <v>284</v>
       </c>
       <c r="E79" t="n">
-        <v>337</v>
+        <v>291</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2105,19 +2105,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>368</v>
+        <v>294</v>
       </c>
       <c r="E80" t="n">
-        <v>378</v>
+        <v>301</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2126,19 +2126,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="E81" t="n">
-        <v>384</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2147,19 +2147,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>329</v>
+        <v>264</v>
       </c>
       <c r="E82" t="n">
-        <v>335</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2168,19 +2168,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="E83" t="n">
-        <v>386</v>
+        <v>299</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="E84" t="n">
-        <v>397</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2210,19 +2210,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D85" t="n">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="E85" t="n">
-        <v>403</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2231,19 +2231,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D86" t="n">
-        <v>335</v>
+        <v>271</v>
       </c>
       <c r="E86" t="n">
-        <v>365</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2255,16 +2255,16 @@
         <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>386</v>
+        <v>299</v>
       </c>
       <c r="E87" t="n">
-        <v>392</v>
+        <v>305</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2273,19 +2273,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D88" t="n">
-        <v>397</v>
+        <v>306</v>
       </c>
       <c r="E88" t="n">
-        <v>422</v>
+        <v>316</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2294,19 +2294,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D89" t="n">
-        <v>422</v>
+        <v>365</v>
       </c>
       <c r="E89" t="n">
-        <v>427</v>
+        <v>382</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D90" t="n">
-        <v>365</v>
+        <v>281</v>
       </c>
       <c r="E90" t="n">
-        <v>392</v>
+        <v>316</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2336,19 +2336,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>392</v>
+        <v>316</v>
       </c>
       <c r="E91" t="n">
-        <v>397</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2360,16 +2360,16 @@
         <v>10</v>
       </c>
       <c r="D92" t="n">
-        <v>422</v>
+        <v>323</v>
       </c>
       <c r="E92" t="n">
-        <v>432</v>
+        <v>333</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2378,19 +2378,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="E93" t="n">
-        <v>457</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2399,19 +2399,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>392</v>
+        <v>316</v>
       </c>
       <c r="E94" t="n">
-        <v>400</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2420,19 +2420,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D95" t="n">
-        <v>400</v>
+        <v>329</v>
       </c>
       <c r="E95" t="n">
-        <v>406</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>432</v>
+        <v>345</v>
       </c>
       <c r="E96" t="n">
-        <v>439</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2462,19 +2462,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D97" t="n">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="E97" t="n">
-        <v>485</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2483,19 +2483,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>400</v>
+        <v>329</v>
       </c>
       <c r="E98" t="n">
-        <v>424</v>
+        <v>337</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2504,19 +2504,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>424</v>
+        <v>345</v>
       </c>
       <c r="E99" t="n">
-        <v>434</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2525,19 +2525,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D100" t="n">
-        <v>439</v>
+        <v>354</v>
       </c>
       <c r="E100" t="n">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2546,19 +2546,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D101" t="n">
-        <v>485</v>
+        <v>416</v>
       </c>
       <c r="E101" t="n">
-        <v>494</v>
+        <v>434</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2567,19 +2567,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>424</v>
+        <v>337</v>
       </c>
       <c r="E102" t="n">
-        <v>443</v>
+        <v>347</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2588,19 +2588,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D103" t="n">
-        <v>443</v>
+        <v>352</v>
       </c>
       <c r="E103" t="n">
-        <v>448</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2609,19 +2609,19 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="E104" t="n">
-        <v>461</v>
+        <v>392</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2630,19 +2630,19 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D105" t="n">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="E105" t="n">
-        <v>526</v>
+        <v>465</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2651,19 +2651,19 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="E106" t="n">
-        <v>465</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2672,19 +2672,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>465</v>
+        <v>380</v>
       </c>
       <c r="E107" t="n">
-        <v>485</v>
+        <v>388</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2693,19 +2693,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D108" t="n">
-        <v>485</v>
+        <v>392</v>
       </c>
       <c r="E108" t="n">
-        <v>494</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2714,19 +2714,19 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D109" t="n">
-        <v>526</v>
+        <v>465</v>
       </c>
       <c r="E109" t="n">
-        <v>537</v>
+        <v>488</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2735,19 +2735,19 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D110" t="n">
-        <v>465</v>
+        <v>355</v>
       </c>
       <c r="E110" t="n">
-        <v>472</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2756,19 +2756,19 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D111" t="n">
-        <v>485</v>
+        <v>388</v>
       </c>
       <c r="E111" t="n">
-        <v>503</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2777,19 +2777,19 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D112" t="n">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="E112" t="n">
-        <v>539</v>
+        <v>441</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2798,19 +2798,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D113" t="n">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="E113" t="n">
-        <v>544</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2819,19 +2819,19 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D114" t="n">
-        <v>472</v>
+        <v>372</v>
       </c>
       <c r="E114" t="n">
-        <v>484</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D115" t="n">
-        <v>503</v>
+        <v>405</v>
       </c>
       <c r="E115" t="n">
-        <v>508</v>
+        <v>418</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2861,19 +2861,19 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D116" t="n">
-        <v>539</v>
+        <v>441</v>
       </c>
       <c r="E116" t="n">
-        <v>545</v>
+        <v>452</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D117" t="n">
-        <v>545</v>
+        <v>505</v>
       </c>
       <c r="E117" t="n">
-        <v>562</v>
+        <v>510</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2903,19 +2903,19 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D118" t="n">
-        <v>484</v>
+        <v>381</v>
       </c>
       <c r="E118" t="n">
-        <v>504</v>
+        <v>398</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2924,19 +2924,19 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D119" t="n">
-        <v>508</v>
+        <v>418</v>
       </c>
       <c r="E119" t="n">
-        <v>530</v>
+        <v>445</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>545</v>
+        <v>452</v>
       </c>
       <c r="E120" t="n">
-        <v>605</v>
+        <v>461</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D121" t="n">
-        <v>605</v>
+        <v>510</v>
       </c>
       <c r="E121" t="n">
-        <v>625</v>
+        <v>539</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2987,19 +2987,19 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D122" t="n">
-        <v>504</v>
+        <v>398</v>
       </c>
       <c r="E122" t="n">
-        <v>510</v>
+        <v>422</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3011,16 +3011,16 @@
         <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>530</v>
+        <v>445</v>
       </c>
       <c r="E123" t="n">
-        <v>536</v>
+        <v>451</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3029,19 +3029,19 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D124" t="n">
-        <v>605</v>
+        <v>461</v>
       </c>
       <c r="E124" t="n">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3053,16 +3053,16 @@
         <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>625</v>
+        <v>539</v>
       </c>
       <c r="E125" t="n">
-        <v>633</v>
+        <v>547</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3071,19 +3071,19 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>510</v>
+        <v>422</v>
       </c>
       <c r="E126" t="n">
-        <v>518</v>
+        <v>428</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3092,19 +3092,19 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D127" t="n">
-        <v>536</v>
+        <v>451</v>
       </c>
       <c r="E127" t="n">
-        <v>553</v>
+        <v>464</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D128" t="n">
-        <v>611</v>
+        <v>466</v>
       </c>
       <c r="E128" t="n">
-        <v>627</v>
+        <v>471</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3134,19 +3134,19 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D129" t="n">
-        <v>633</v>
+        <v>547</v>
       </c>
       <c r="E129" t="n">
-        <v>639</v>
+        <v>552</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3155,19 +3155,19 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D130" t="n">
-        <v>518</v>
+        <v>428</v>
       </c>
       <c r="E130" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D131" t="n">
-        <v>553</v>
+        <v>488</v>
       </c>
       <c r="E131" t="n">
-        <v>572</v>
+        <v>503</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3197,19 +3197,19 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D132" t="n">
-        <v>627</v>
+        <v>503</v>
       </c>
       <c r="E132" t="n">
-        <v>647</v>
+        <v>517</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3218,19 +3218,19 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D133" t="n">
-        <v>647</v>
+        <v>552</v>
       </c>
       <c r="E133" t="n">
-        <v>665</v>
+        <v>562</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3239,19 +3239,19 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D134" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="E134" t="n">
-        <v>543</v>
+        <v>507</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3260,19 +3260,19 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D135" t="n">
-        <v>572</v>
+        <v>507</v>
       </c>
       <c r="E135" t="n">
-        <v>583</v>
+        <v>516</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3281,19 +3281,19 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
-        <v>647</v>
+        <v>517</v>
       </c>
       <c r="E136" t="n">
-        <v>677</v>
+        <v>523</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>677</v>
+        <v>562</v>
       </c>
       <c r="E137" t="n">
-        <v>691</v>
+        <v>569</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3323,19 +3323,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D138" t="n">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="E138" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3344,19 +3344,19 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D139" t="n">
-        <v>583</v>
+        <v>535</v>
       </c>
       <c r="E139" t="n">
-        <v>588</v>
+        <v>546</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3365,19 +3365,19 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D140" t="n">
-        <v>677</v>
+        <v>546</v>
       </c>
       <c r="E140" t="n">
-        <v>694</v>
+        <v>554</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3386,19 +3386,19 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D141" t="n">
-        <v>694</v>
+        <v>569</v>
       </c>
       <c r="E141" t="n">
-        <v>708</v>
+        <v>586</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3407,19 +3407,19 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D142" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="E142" t="n">
-        <v>586</v>
+        <v>547</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D143" t="n">
-        <v>588</v>
+        <v>547</v>
       </c>
       <c r="E143" t="n">
-        <v>610</v>
+        <v>558</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3449,19 +3449,19 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D144" t="n">
-        <v>694</v>
+        <v>558</v>
       </c>
       <c r="E144" t="n">
-        <v>728</v>
+        <v>576</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3470,19 +3470,19 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D145" t="n">
-        <v>728</v>
+        <v>586</v>
       </c>
       <c r="E145" t="n">
-        <v>788</v>
+        <v>600</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3491,19 +3491,19 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D146" t="n">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="E146" t="n">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3512,19 +3512,19 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D147" t="n">
-        <v>610</v>
+        <v>578</v>
       </c>
       <c r="E147" t="n">
-        <v>670</v>
+        <v>584</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D148" t="n">
-        <v>728</v>
+        <v>584</v>
       </c>
       <c r="E148" t="n">
-        <v>736</v>
+        <v>614</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3554,19 +3554,19 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D149" t="n">
-        <v>788</v>
+        <v>614</v>
       </c>
       <c r="E149" t="n">
-        <v>793</v>
+        <v>643</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3578,16 +3578,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="E150" t="n">
-        <v>607</v>
+        <v>587</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3596,19 +3596,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D151" t="n">
-        <v>670</v>
+        <v>587</v>
       </c>
       <c r="E151" t="n">
-        <v>675</v>
+        <v>604</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3617,19 +3617,19 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D152" t="n">
-        <v>736</v>
+        <v>614</v>
       </c>
       <c r="E152" t="n">
-        <v>752</v>
+        <v>619</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3638,19 +3638,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D153" t="n">
-        <v>793</v>
+        <v>643</v>
       </c>
       <c r="E153" t="n">
-        <v>809</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3659,19 +3659,19 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D154" t="n">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="E154" t="n">
-        <v>635</v>
+        <v>592</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3680,19 +3680,19 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D155" t="n">
-        <v>675</v>
+        <v>604</v>
       </c>
       <c r="E155" t="n">
-        <v>692</v>
+        <v>614</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3701,19 +3701,19 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>752</v>
+        <v>619</v>
       </c>
       <c r="E156" t="n">
-        <v>773</v>
+        <v>629</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3722,19 +3722,19 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D157" t="n">
-        <v>809</v>
+        <v>654</v>
       </c>
       <c r="E157" t="n">
-        <v>837</v>
+        <v>688</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D158" t="n">
-        <v>635</v>
+        <v>592</v>
       </c>
       <c r="E158" t="n">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3764,19 +3764,19 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D159" t="n">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="E159" t="n">
-        <v>698</v>
+        <v>662</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3785,19 +3785,19 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D160" t="n">
-        <v>773</v>
+        <v>662</v>
       </c>
       <c r="E160" t="n">
-        <v>807</v>
+        <v>673</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3806,19 +3806,19 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D161" t="n">
-        <v>837</v>
+        <v>688</v>
       </c>
       <c r="E161" t="n">
-        <v>858</v>
+        <v>719</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3827,19 +3827,19 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E162" t="n">
-        <v>688</v>
+        <v>659</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3848,19 +3848,19 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D163" t="n">
-        <v>698</v>
+        <v>662</v>
       </c>
       <c r="E163" t="n">
-        <v>706</v>
+        <v>674</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3869,19 +3869,19 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D164" t="n">
-        <v>807</v>
+        <v>674</v>
       </c>
       <c r="E164" t="n">
-        <v>833</v>
+        <v>681</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3890,19 +3890,19 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D165" t="n">
-        <v>858</v>
+        <v>719</v>
       </c>
       <c r="E165" t="n">
-        <v>876</v>
+        <v>727</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3911,19 +3911,19 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D166" t="n">
-        <v>688</v>
+        <v>659</v>
       </c>
       <c r="E166" t="n">
-        <v>697</v>
+        <v>670</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3932,19 +3932,19 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D167" t="n">
-        <v>706</v>
+        <v>674</v>
       </c>
       <c r="E167" t="n">
-        <v>716</v>
+        <v>682</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3953,19 +3953,19 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D168" t="n">
-        <v>833</v>
+        <v>682</v>
       </c>
       <c r="E168" t="n">
-        <v>885</v>
+        <v>724</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3974,19 +3974,19 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D169" t="n">
-        <v>885</v>
+        <v>727</v>
       </c>
       <c r="E169" t="n">
-        <v>897</v>
+        <v>742</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3995,19 +3995,19 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D170" t="n">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="E170" t="n">
-        <v>709</v>
+        <v>689</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4016,19 +4016,19 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D171" t="n">
-        <v>716</v>
+        <v>689</v>
       </c>
       <c r="E171" t="n">
-        <v>723</v>
+        <v>707</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4037,19 +4037,19 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D172" t="n">
-        <v>885</v>
+        <v>724</v>
       </c>
       <c r="E172" t="n">
-        <v>900</v>
+        <v>730</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D173" t="n">
-        <v>900</v>
+        <v>742</v>
       </c>
       <c r="E173" t="n">
-        <v>934</v>
+        <v>753</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4079,19 +4079,19 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D174" t="n">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="E174" t="n">
-        <v>715</v>
+        <v>699</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4100,19 +4100,19 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D175" t="n">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="E175" t="n">
-        <v>735</v>
+        <v>724</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4121,19 +4121,19 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D176" t="n">
-        <v>900</v>
+        <v>730</v>
       </c>
       <c r="E176" t="n">
-        <v>905</v>
+        <v>738</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4142,19 +4142,19 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D177" t="n">
-        <v>934</v>
+        <v>753</v>
       </c>
       <c r="E177" t="n">
-        <v>950</v>
+        <v>763</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4163,19 +4163,19 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D178" t="n">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="E178" t="n">
-        <v>725</v>
+        <v>718</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4184,19 +4184,19 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D179" t="n">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="E179" t="n">
-        <v>747</v>
+        <v>732</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4205,19 +4205,19 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D180" t="n">
-        <v>905</v>
+        <v>738</v>
       </c>
       <c r="E180" t="n">
-        <v>922</v>
+        <v>750</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4226,19 +4226,19 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D181" t="n">
-        <v>950</v>
+        <v>763</v>
       </c>
       <c r="E181" t="n">
-        <v>962</v>
+        <v>771</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4247,19 +4247,19 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="E182" t="n">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4268,19 +4268,19 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D183" t="n">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="E183" t="n">
-        <v>758</v>
+        <v>745</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4289,19 +4289,19 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D184" t="n">
-        <v>922</v>
+        <v>750</v>
       </c>
       <c r="E184" t="n">
-        <v>946</v>
+        <v>782</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4310,19 +4310,19 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D185" t="n">
-        <v>962</v>
+        <v>782</v>
       </c>
       <c r="E185" t="n">
-        <v>981</v>
+        <v>787</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D186" t="n">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="E186" t="n">
         <v>760</v>
@@ -4343,7 +4343,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4352,19 +4352,19 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D187" t="n">
         <v>760</v>
       </c>
       <c r="E187" t="n">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4373,19 +4373,19 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D188" t="n">
-        <v>946</v>
+        <v>782</v>
       </c>
       <c r="E188" t="n">
-        <v>971</v>
+        <v>792</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4394,19 +4394,19 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D189" t="n">
-        <v>981</v>
+        <v>792</v>
       </c>
       <c r="E189" t="n">
-        <v>990</v>
+        <v>802</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4415,19 +4415,19 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D190" t="n">
         <v>760</v>
       </c>
       <c r="E190" t="n">
-        <v>781</v>
+        <v>789</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4436,19 +4436,19 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D191" t="n">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="E191" t="n">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4457,19 +4457,19 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D192" t="n">
-        <v>971</v>
+        <v>795</v>
       </c>
       <c r="E192" t="n">
-        <v>1006</v>
+        <v>822</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D193" t="n">
-        <v>1006</v>
+        <v>822</v>
       </c>
       <c r="E193" t="n">
-        <v>1037</v>
+        <v>827</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4499,19 +4499,19 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D194" t="n">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="E194" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4520,19 +4520,19 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D195" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E195" t="n">
-        <v>813</v>
+        <v>833</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4541,19 +4541,19 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D196" t="n">
-        <v>1006</v>
+        <v>833</v>
       </c>
       <c r="E196" t="n">
-        <v>1014</v>
+        <v>849</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4562,19 +4562,19 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D197" t="n">
-        <v>1037</v>
+        <v>849</v>
       </c>
       <c r="E197" t="n">
-        <v>1042</v>
+        <v>909</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4583,19 +4583,19 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D198" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E198" t="n">
-        <v>811</v>
+        <v>819</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4604,19 +4604,19 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D199" t="n">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="E199" t="n">
-        <v>858</v>
+        <v>843</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4625,19 +4625,19 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D200" t="n">
-        <v>1014</v>
+        <v>849</v>
       </c>
       <c r="E200" t="n">
-        <v>1038</v>
+        <v>863</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4646,13 +4646,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D201" t="n">
-        <v>1042</v>
+        <v>909</v>
       </c>
       <c r="E201" t="n">
-        <v>1067</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
